--- a/artfynd/A 51425-2023 artfynd.xlsx
+++ b/artfynd/A 51425-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 51425-2023 artfynd.xlsx
+++ b/artfynd/A 51425-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY89"/>
+  <dimension ref="A1:AY94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>17270895</v>
+        <v>120724708</v>
       </c>
       <c r="B2" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,41 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Motmyran, Jmt</t>
+          <t>Lungsjön, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>563672.99512258</v>
+        <v>563603</v>
       </c>
       <c r="R2" t="n">
-        <v>6968822.422955421</v>
+        <v>6968864</v>
       </c>
       <c r="S2" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2014-11-26</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2014-11-26</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-26</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,82 +756,64 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Caroline Westerlund</t>
+          <t>Erica Hästdahl</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Via Caroline Westerlund</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>17270900</v>
+        <v>120724709</v>
       </c>
       <c r="B3" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Motmyran, Jmt</t>
+          <t>Lungsjön, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563672.99512258</v>
+        <v>563475</v>
       </c>
       <c r="R3" t="n">
-        <v>6968822.422955421</v>
+        <v>6968878</v>
       </c>
       <c r="S3" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -874,22 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2014-11-26</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2014-11-26</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-26</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -900,40 +853,26 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Caroline Westerlund</t>
+          <t>Erica Hästdahl</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Via Caroline Westerlund</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>17270902</v>
+        <v>120724723</v>
       </c>
       <c r="B4" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -941,41 +880,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Motmyran, Jmt</t>
+          <t>Lungsjön, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563672.99512258</v>
+        <v>563520</v>
       </c>
       <c r="R4" t="n">
-        <v>6968822.422955421</v>
+        <v>6968899</v>
       </c>
       <c r="S4" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -999,22 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2014-11-26</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-26</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2014-11-26</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-26</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1025,82 +950,64 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Caroline Westerlund</t>
+          <t>Erica Hästdahl</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Via Caroline Westerlund</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>17270891</v>
+        <v>120724789</v>
       </c>
       <c r="B5" t="n">
-        <v>78503</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92509</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6456</v>
+        <v>760</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Motmyran, Jmt</t>
+          <t>Lungsjön, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>563672.99512258</v>
+        <v>563829</v>
       </c>
       <c r="R5" t="n">
-        <v>6968822.422955421</v>
+        <v>6968692</v>
       </c>
       <c r="S5" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1124,22 +1031,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2014-11-26</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2014-11-26</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-26</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1150,40 +1047,26 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Caroline Westerlund</t>
+          <t>Erica Hästdahl</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Via Caroline Westerlund</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>111966023</v>
+        <v>120724707</v>
       </c>
       <c r="B6" t="n">
-        <v>90830</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91460</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1191,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2059</v>
+        <v>937</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Vit vedfingersvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Lentaria epichnoa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.) Corner</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1215,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>563798</v>
+        <v>563600</v>
       </c>
       <c r="R6" t="n">
-        <v>6968889</v>
+        <v>6968906</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1245,12 +1128,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-09-08</t>
+          <t>2024-09-26</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-09-08</t>
+          <t>2024-09-26</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1277,15 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120724711</v>
+        <v>120724710</v>
       </c>
       <c r="B7" t="n">
-        <v>90682</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1317,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>563732</v>
+        <v>563728</v>
       </c>
       <c r="R7" t="n">
-        <v>6968777</v>
+        <v>6968783</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1379,15 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120724738</v>
+        <v>120724711</v>
       </c>
       <c r="B8" t="n">
-        <v>79677</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1395,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1419,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>563489</v>
+        <v>563732</v>
       </c>
       <c r="R8" t="n">
-        <v>6968872</v>
+        <v>6968777</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1481,15 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120724733</v>
+        <v>120724712</v>
       </c>
       <c r="B9" t="n">
-        <v>79677</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1497,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1521,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>563565</v>
+        <v>563544</v>
       </c>
       <c r="R9" t="n">
-        <v>6968852</v>
+        <v>6968882</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1583,37 +1451,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120724748</v>
+        <v>111966014</v>
       </c>
       <c r="B10" t="n">
-        <v>79677</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>2059</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1623,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>563593</v>
+        <v>563815</v>
       </c>
       <c r="R10" t="n">
-        <v>6968905</v>
+        <v>6968801</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1653,12 +1516,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2023-09-08</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2023-09-08</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1685,37 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120724744</v>
+        <v>111966023</v>
       </c>
       <c r="B11" t="n">
-        <v>79677</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>2059</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1725,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>563509</v>
+        <v>563798</v>
       </c>
       <c r="R11" t="n">
-        <v>6968917</v>
+        <v>6968889</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1755,12 +1613,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2023-09-08</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2023-09-08</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1787,37 +1645,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120724735</v>
+        <v>120724718</v>
       </c>
       <c r="B12" t="n">
-        <v>79677</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>2059</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1827,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>563543</v>
+        <v>563816</v>
       </c>
       <c r="R12" t="n">
-        <v>6968853</v>
+        <v>6968798</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1889,37 +1742,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120724787</v>
+        <v>120724719</v>
       </c>
       <c r="B13" t="n">
-        <v>91958</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1929,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>563584</v>
+        <v>563727</v>
       </c>
       <c r="R13" t="n">
-        <v>6968918</v>
+        <v>6968900</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1991,15 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120724788</v>
+        <v>120724791</v>
       </c>
       <c r="B14" t="n">
-        <v>91958</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97231</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2007,21 +1850,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>2869</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2031,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>563736</v>
+        <v>563801</v>
       </c>
       <c r="R14" t="n">
-        <v>6968897</v>
+        <v>6968737</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2093,37 +1936,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120724723</v>
+        <v>120724792</v>
       </c>
       <c r="B15" t="n">
-        <v>90968</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97231</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>658</v>
+        <v>2869</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2133,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>563520</v>
+        <v>563461</v>
       </c>
       <c r="R15" t="n">
-        <v>6968899</v>
+        <v>6968880</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2195,15 +2033,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120724778</v>
+        <v>120724793</v>
       </c>
       <c r="B16" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2211,21 +2044,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>4362</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2235,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>563512</v>
+        <v>563813</v>
       </c>
       <c r="R16" t="n">
-        <v>6968877</v>
+        <v>6968930</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2297,15 +2130,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120724780</v>
+        <v>111966057</v>
       </c>
       <c r="B17" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2313,21 +2141,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2337,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>563614</v>
+        <v>563817</v>
       </c>
       <c r="R17" t="n">
-        <v>6968898</v>
+        <v>6968801</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2367,12 +2195,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2023-09-08</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2023-09-08</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2399,15 +2227,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120724774</v>
+        <v>120724785</v>
       </c>
       <c r="B18" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2415,21 +2238,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2439,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>563592</v>
+        <v>563739</v>
       </c>
       <c r="R18" t="n">
-        <v>6968874</v>
+        <v>6968894</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2501,37 +2324,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120724757</v>
+        <v>120724786</v>
       </c>
       <c r="B19" t="n">
-        <v>79637</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>229497</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2541,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>563709</v>
+        <v>563766</v>
       </c>
       <c r="R19" t="n">
-        <v>6968788</v>
+        <v>6968816</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2603,37 +2421,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120724766</v>
+        <v>120724787</v>
       </c>
       <c r="B20" t="n">
-        <v>79643</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>229748</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2643,10 +2456,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>563783</v>
+        <v>563584</v>
       </c>
       <c r="R20" t="n">
-        <v>6968772</v>
+        <v>6968918</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2705,37 +2518,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120724792</v>
+        <v>120724788</v>
       </c>
       <c r="B21" t="n">
-        <v>95353</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2869</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2745,10 +2553,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>563461</v>
+        <v>563736</v>
       </c>
       <c r="R21" t="n">
-        <v>6968880</v>
+        <v>6968897</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2807,37 +2615,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120724777</v>
+        <v>120724716</v>
       </c>
       <c r="B22" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93201</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>4365</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2847,10 +2650,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>563530</v>
+        <v>563659</v>
       </c>
       <c r="R22" t="n">
-        <v>6968861</v>
+        <v>6968821</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2891,6 +2694,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2909,15 +2713,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120724751</v>
+        <v>120724704</v>
       </c>
       <c r="B23" t="n">
-        <v>79677</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89156</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2925,21 +2724,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>4412</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2949,10 +2748,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>563752</v>
+        <v>563529</v>
       </c>
       <c r="R23" t="n">
-        <v>6968894</v>
+        <v>6968899</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3011,37 +2810,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120724742</v>
+        <v>120724794</v>
       </c>
       <c r="B24" t="n">
-        <v>79677</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91966</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>5321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3051,10 +2845,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>563485</v>
+        <v>563553</v>
       </c>
       <c r="R24" t="n">
-        <v>6968899</v>
+        <v>6968900</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3095,6 +2889,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3113,15 +2908,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120724706</v>
+        <v>111965995</v>
       </c>
       <c r="B25" t="n">
-        <v>74704</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3129,21 +2919,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6440</v>
+        <v>5442</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3153,10 +2943,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>563579</v>
+        <v>563867</v>
       </c>
       <c r="R25" t="n">
-        <v>6968912</v>
+        <v>6968750</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3183,12 +2973,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2023-09-08</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2023-09-08</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3215,37 +3005,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120724734</v>
+        <v>111966048</v>
       </c>
       <c r="B26" t="n">
-        <v>79677</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90691</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>6276</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3255,10 +3040,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>563558</v>
+        <v>563827</v>
       </c>
       <c r="R26" t="n">
-        <v>6968855</v>
+        <v>6968837</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3285,12 +3070,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2023-09-08</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2023-09-08</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3317,53 +3102,52 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120724759</v>
+        <v>17270902</v>
       </c>
       <c r="B27" t="n">
-        <v>79637</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Lungsjön, Jmt</t>
+          <t>Motmyran, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>563518</v>
+        <v>563673</v>
       </c>
       <c r="R27" t="n">
-        <v>6968916</v>
+        <v>6968822</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3387,12 +3171,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2014-11-26</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2014-11-26</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3403,53 +3187,57 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Caroline Westerlund</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
-        </is>
-      </c>
-      <c r="AY27" t="inlineStr"/>
+          <t>Via Caroline Westerlund</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120724732</v>
+        <v>120724767</v>
       </c>
       <c r="B28" t="n">
-        <v>79677</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3459,10 +3247,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>563710</v>
+        <v>563777</v>
       </c>
       <c r="R28" t="n">
-        <v>6968787</v>
+        <v>6968833</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3521,37 +3309,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120724753</v>
+        <v>120724768</v>
       </c>
       <c r="B29" t="n">
-        <v>79713</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3561,10 +3344,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>563658</v>
+        <v>563727</v>
       </c>
       <c r="R29" t="n">
-        <v>6968873</v>
+        <v>6968840</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3623,37 +3406,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120724705</v>
+        <v>120724769</v>
       </c>
       <c r="B30" t="n">
-        <v>74704</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3663,10 +3441,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>563580</v>
+        <v>563748</v>
       </c>
       <c r="R30" t="n">
-        <v>6968880</v>
+        <v>6968812</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3725,37 +3503,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120724761</v>
+        <v>120724771</v>
       </c>
       <c r="B31" t="n">
-        <v>78332</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3765,10 +3538,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>563711</v>
+        <v>563745</v>
       </c>
       <c r="R31" t="n">
-        <v>6968858</v>
+        <v>6968764</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3827,37 +3600,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120724785</v>
+        <v>120724772</v>
       </c>
       <c r="B32" t="n">
-        <v>91958</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3867,10 +3635,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>563739</v>
+        <v>563671</v>
       </c>
       <c r="R32" t="n">
-        <v>6968894</v>
+        <v>6968786</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3932,16 +3700,11 @@
         <v>120724773</v>
       </c>
       <c r="B33" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
@@ -4031,37 +3794,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120724737</v>
+        <v>120724774</v>
       </c>
       <c r="B34" t="n">
-        <v>79677</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4071,10 +3829,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>563514</v>
+        <v>563592</v>
       </c>
       <c r="R34" t="n">
-        <v>6968885</v>
+        <v>6968874</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4133,37 +3891,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120724730</v>
+        <v>120724775</v>
       </c>
       <c r="B35" t="n">
-        <v>79677</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4173,10 +3926,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>563784</v>
+        <v>563578</v>
       </c>
       <c r="R35" t="n">
-        <v>6968771</v>
+        <v>6968868</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4235,37 +3988,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120724745</v>
+        <v>120724776</v>
       </c>
       <c r="B36" t="n">
-        <v>79677</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4275,10 +4023,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>563518</v>
+        <v>563576</v>
       </c>
       <c r="R36" t="n">
-        <v>6968916</v>
+        <v>6968857</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4337,37 +4085,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120724721</v>
+        <v>120724777</v>
       </c>
       <c r="B37" t="n">
-        <v>79581</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4377,10 +4120,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>563514</v>
+        <v>563530</v>
       </c>
       <c r="R37" t="n">
-        <v>6968885</v>
+        <v>6968861</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4439,37 +4182,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120724794</v>
+        <v>120724778</v>
       </c>
       <c r="B38" t="n">
-        <v>90732</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5321</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4479,10 +4217,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>563553</v>
+        <v>563512</v>
       </c>
       <c r="R38" t="n">
-        <v>6968900</v>
+        <v>6968877</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4523,7 +4261,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4545,16 +4282,11 @@
         <v>120724779</v>
       </c>
       <c r="B39" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
@@ -4644,37 +4376,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120724726</v>
+        <v>120724780</v>
       </c>
       <c r="B40" t="n">
-        <v>79677</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4684,10 +4411,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>563762</v>
+        <v>563614</v>
       </c>
       <c r="R40" t="n">
-        <v>6968907</v>
+        <v>6968898</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4746,37 +4473,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120724758</v>
+        <v>120724781</v>
       </c>
       <c r="B41" t="n">
-        <v>79637</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4786,10 +4508,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>563565</v>
+        <v>563658</v>
       </c>
       <c r="R41" t="n">
-        <v>6968852</v>
+        <v>6968875</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4848,37 +4570,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120724727</v>
+        <v>120724782</v>
       </c>
       <c r="B42" t="n">
-        <v>79677</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4888,10 +4605,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>563727</v>
+        <v>563673</v>
       </c>
       <c r="R42" t="n">
-        <v>6968840</v>
+        <v>6968881</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4950,37 +4667,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120724750</v>
+        <v>120724783</v>
       </c>
       <c r="B43" t="n">
-        <v>79677</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4990,10 +4702,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>563658</v>
+        <v>563692</v>
       </c>
       <c r="R43" t="n">
-        <v>6968873</v>
+        <v>6968897</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5052,19 +4764,14 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120724772</v>
+        <v>120724784</v>
       </c>
       <c r="B44" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
@@ -5092,10 +4799,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>563671</v>
+        <v>563727</v>
       </c>
       <c r="R44" t="n">
-        <v>6968786</v>
+        <v>6968900</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5154,15 +4861,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120724714</v>
+        <v>120724705</v>
       </c>
       <c r="B45" t="n">
-        <v>57348</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5170,21 +4872,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5194,10 +4896,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>563553</v>
+        <v>563580</v>
       </c>
       <c r="R45" t="n">
-        <v>6968908</v>
+        <v>6968880</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5256,15 +4958,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120724715</v>
+        <v>120724706</v>
       </c>
       <c r="B46" t="n">
-        <v>57348</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5272,21 +4969,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5296,10 +4993,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>563776</v>
+        <v>563579</v>
       </c>
       <c r="R46" t="n">
-        <v>6968899</v>
+        <v>6968912</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5358,37 +5055,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120724716</v>
+        <v>120724761</v>
       </c>
       <c r="B47" t="n">
-        <v>91962</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4365</v>
+        <v>6446</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5398,10 +5090,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>563659</v>
+        <v>563711</v>
       </c>
       <c r="R47" t="n">
-        <v>6968821</v>
+        <v>6968858</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5442,7 +5134,6 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5461,53 +5152,52 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120724710</v>
+        <v>17270891</v>
       </c>
       <c r="B48" t="n">
-        <v>90682</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>6456</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Lungsjön, Jmt</t>
+          <t>Motmyran, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>563728</v>
+        <v>563673</v>
       </c>
       <c r="R48" t="n">
-        <v>6968783</v>
+        <v>6968822</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5531,12 +5221,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2014-11-26</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2014-11-26</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5547,31 +5237,35 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
+      </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Caroline Westerlund</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
-        </is>
-      </c>
-      <c r="AY48" t="inlineStr"/>
+          <t>Via Caroline Westerlund</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120724724</v>
+        <v>120724720</v>
       </c>
       <c r="B49" t="n">
-        <v>79705</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5579,21 +5273,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6461</v>
+        <v>6456</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5603,10 +5297,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>563766</v>
+        <v>563709</v>
       </c>
       <c r="R49" t="n">
-        <v>6968816</v>
+        <v>6968788</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5665,37 +5359,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120724708</v>
+        <v>120724721</v>
       </c>
       <c r="B50" t="n">
-        <v>95606</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>53</v>
+        <v>6456</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5705,10 +5394,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>563603</v>
+        <v>563514</v>
       </c>
       <c r="R50" t="n">
-        <v>6968864</v>
+        <v>6968885</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5767,37 +5456,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120724707</v>
+        <v>120724722</v>
       </c>
       <c r="B51" t="n">
-        <v>90243</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>937</v>
+        <v>6456</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vit vedfingersvamp</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lentaria epichnoa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Corner</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5807,10 +5491,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>563600</v>
+        <v>563493</v>
       </c>
       <c r="R51" t="n">
-        <v>6968906</v>
+        <v>6968901</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5869,15 +5553,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120724712</v>
+        <v>17270895</v>
       </c>
       <c r="B52" t="n">
-        <v>90682</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5885,37 +5564,41 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Lungsjön, Jmt</t>
+          <t>Motmyran, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>563544</v>
+        <v>563673</v>
       </c>
       <c r="R52" t="n">
-        <v>6968882</v>
+        <v>6968822</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5939,12 +5622,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2014-11-26</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2014-11-26</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5955,31 +5638,35 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
+      </c>
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Caroline Westerlund</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
-        </is>
-      </c>
-      <c r="AY52" t="inlineStr"/>
+          <t>Via Caroline Westerlund</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120724719</v>
+        <v>120724726</v>
       </c>
       <c r="B53" t="n">
-        <v>91974</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5987,21 +5674,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>2059</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6011,10 +5698,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>563727</v>
+        <v>563762</v>
       </c>
       <c r="R53" t="n">
-        <v>6968900</v>
+        <v>6968907</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6073,37 +5760,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120724791</v>
+        <v>120724727</v>
       </c>
       <c r="B54" t="n">
-        <v>95353</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>2869</v>
+        <v>6458</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6113,10 +5795,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>563801</v>
+        <v>563727</v>
       </c>
       <c r="R54" t="n">
-        <v>6968737</v>
+        <v>6968840</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6175,15 +5857,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120724740</v>
+        <v>120724728</v>
       </c>
       <c r="B55" t="n">
-        <v>79677</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6215,10 +5892,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>563466</v>
+        <v>563741</v>
       </c>
       <c r="R55" t="n">
-        <v>6968889</v>
+        <v>6968836</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6280,12 +5957,7 @@
         <v>120724729</v>
       </c>
       <c r="B56" t="n">
-        <v>79677</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6379,15 +6051,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120724771</v>
+        <v>120724730</v>
       </c>
       <c r="B57" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6395,21 +6062,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6419,10 +6086,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>563745</v>
+        <v>563784</v>
       </c>
       <c r="R57" t="n">
-        <v>6968764</v>
+        <v>6968771</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6481,15 +6148,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120724739</v>
+        <v>120724731</v>
       </c>
       <c r="B58" t="n">
-        <v>79677</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6521,10 +6183,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>563448</v>
+        <v>563756</v>
       </c>
       <c r="R58" t="n">
-        <v>6968903</v>
+        <v>6968771</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6583,15 +6245,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120724713</v>
+        <v>120724732</v>
       </c>
       <c r="B59" t="n">
-        <v>57348</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6599,21 +6256,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6623,10 +6280,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>563593</v>
+        <v>563710</v>
       </c>
       <c r="R59" t="n">
-        <v>6968873</v>
+        <v>6968787</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6685,37 +6342,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120724763</v>
+        <v>120724733</v>
       </c>
       <c r="B60" t="n">
-        <v>98059</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6725,10 +6377,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>563494</v>
+        <v>563565</v>
       </c>
       <c r="R60" t="n">
-        <v>6968888</v>
+        <v>6968852</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6787,15 +6439,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120724775</v>
+        <v>120724734</v>
       </c>
       <c r="B61" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6803,21 +6450,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6827,10 +6474,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>563578</v>
+        <v>563558</v>
       </c>
       <c r="R61" t="n">
-        <v>6968868</v>
+        <v>6968855</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6889,37 +6536,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120724722</v>
+        <v>120724735</v>
       </c>
       <c r="B62" t="n">
-        <v>79581</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6929,10 +6571,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>563493</v>
+        <v>563543</v>
       </c>
       <c r="R62" t="n">
-        <v>6968901</v>
+        <v>6968853</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6991,15 +6633,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120724768</v>
+        <v>120724736</v>
       </c>
       <c r="B63" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7007,21 +6644,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7031,10 +6668,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>563727</v>
+        <v>563544</v>
       </c>
       <c r="R63" t="n">
-        <v>6968840</v>
+        <v>6968860</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7093,15 +6730,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120724743</v>
+        <v>120724737</v>
       </c>
       <c r="B64" t="n">
-        <v>79677</v>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7133,10 +6765,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>563507</v>
+        <v>563514</v>
       </c>
       <c r="R64" t="n">
-        <v>6968907</v>
+        <v>6968885</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7195,15 +6827,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120724736</v>
+        <v>120724738</v>
       </c>
       <c r="B65" t="n">
-        <v>79677</v>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7235,10 +6862,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>563544</v>
+        <v>563489</v>
       </c>
       <c r="R65" t="n">
-        <v>6968860</v>
+        <v>6968872</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7297,15 +6924,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120724752</v>
+        <v>120724739</v>
       </c>
       <c r="B66" t="n">
-        <v>79677</v>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7337,10 +6959,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>563770</v>
+        <v>563448</v>
       </c>
       <c r="R66" t="n">
-        <v>6968894</v>
+        <v>6968903</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7399,15 +7021,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120724782</v>
+        <v>120724740</v>
       </c>
       <c r="B67" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7415,21 +7032,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7439,10 +7056,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>563673</v>
+        <v>563466</v>
       </c>
       <c r="R67" t="n">
-        <v>6968881</v>
+        <v>6968889</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7501,15 +7118,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120724784</v>
+        <v>120724741</v>
       </c>
       <c r="B68" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7517,21 +7129,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7541,10 +7153,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>563727</v>
+        <v>563480</v>
       </c>
       <c r="R68" t="n">
-        <v>6968900</v>
+        <v>6968888</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7603,15 +7215,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120724718</v>
+        <v>120724742</v>
       </c>
       <c r="B69" t="n">
-        <v>91974</v>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7619,21 +7226,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>2059</v>
+        <v>6458</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7643,10 +7250,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>563816</v>
+        <v>563485</v>
       </c>
       <c r="R69" t="n">
-        <v>6968798</v>
+        <v>6968899</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7705,15 +7312,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120724776</v>
+        <v>120724743</v>
       </c>
       <c r="B70" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7721,21 +7323,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7745,10 +7347,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>563576</v>
+        <v>563507</v>
       </c>
       <c r="R70" t="n">
-        <v>6968857</v>
+        <v>6968907</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7807,15 +7409,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120724747</v>
+        <v>120724744</v>
       </c>
       <c r="B71" t="n">
-        <v>79677</v>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7847,10 +7444,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>563553</v>
+        <v>563509</v>
       </c>
       <c r="R71" t="n">
-        <v>6968900</v>
+        <v>6968917</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7909,15 +7506,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120724783</v>
+        <v>120724745</v>
       </c>
       <c r="B72" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7925,21 +7517,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7949,10 +7541,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>563692</v>
+        <v>563518</v>
       </c>
       <c r="R72" t="n">
-        <v>6968897</v>
+        <v>6968916</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8011,15 +7603,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120724728</v>
+        <v>120724746</v>
       </c>
       <c r="B73" t="n">
-        <v>79677</v>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8051,10 +7638,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>563741</v>
+        <v>563545</v>
       </c>
       <c r="R73" t="n">
-        <v>6968836</v>
+        <v>6968898</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8113,37 +7700,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120724786</v>
+        <v>120724747</v>
       </c>
       <c r="B74" t="n">
-        <v>91958</v>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8153,10 +7735,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>563766</v>
+        <v>563553</v>
       </c>
       <c r="R74" t="n">
-        <v>6968816</v>
+        <v>6968900</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8215,15 +7797,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120724749</v>
+        <v>120724748</v>
       </c>
       <c r="B75" t="n">
-        <v>79677</v>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8255,10 +7832,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>563617</v>
+        <v>563593</v>
       </c>
       <c r="R75" t="n">
-        <v>6968907</v>
+        <v>6968905</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8317,37 +7894,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>120724762</v>
+        <v>120724749</v>
       </c>
       <c r="B76" t="n">
-        <v>98059</v>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8357,10 +7929,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>563548</v>
+        <v>563617</v>
       </c>
       <c r="R76" t="n">
-        <v>6968851</v>
+        <v>6968907</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8419,15 +7991,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>120724731</v>
+        <v>120724750</v>
       </c>
       <c r="B77" t="n">
-        <v>79677</v>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8459,10 +8026,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>563756</v>
+        <v>563658</v>
       </c>
       <c r="R77" t="n">
-        <v>6968771</v>
+        <v>6968873</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8521,15 +8088,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120724746</v>
+        <v>120724751</v>
       </c>
       <c r="B78" t="n">
-        <v>79677</v>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8561,10 +8123,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>563545</v>
+        <v>563752</v>
       </c>
       <c r="R78" t="n">
-        <v>6968898</v>
+        <v>6968894</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8623,15 +8185,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120724704</v>
+        <v>120724752</v>
       </c>
       <c r="B79" t="n">
-        <v>88532</v>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8639,21 +8196,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>4412</v>
+        <v>6458</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8663,10 +8220,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>563529</v>
+        <v>563770</v>
       </c>
       <c r="R79" t="n">
-        <v>6968899</v>
+        <v>6968894</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8725,37 +8282,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120724767</v>
+        <v>120724724</v>
       </c>
       <c r="B80" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80460</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8765,10 +8317,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>563777</v>
+        <v>563766</v>
       </c>
       <c r="R80" t="n">
-        <v>6968833</v>
+        <v>6968816</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8827,15 +8379,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120724720</v>
+        <v>17270900</v>
       </c>
       <c r="B81" t="n">
-        <v>79581</v>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8843,37 +8390,41 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6456</v>
+        <v>6462</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr"/>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Lungsjön, Jmt</t>
+          <t>Motmyran, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>563709</v>
+        <v>563673</v>
       </c>
       <c r="R81" t="n">
-        <v>6968788</v>
+        <v>6968822</v>
       </c>
       <c r="S81" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -8897,12 +8448,12 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2014-11-26</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2014-11-26</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8913,48 +8464,52 @@
       </c>
       <c r="AG81" t="b">
         <v>0</v>
+      </c>
+      <c r="AI81" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Caroline Westerlund</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
-        </is>
-      </c>
-      <c r="AY81" t="inlineStr"/>
+          <t>Via Caroline Westerlund</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120724781</v>
+        <v>120724790</v>
       </c>
       <c r="B82" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -8969,10 +8524,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>563658</v>
+        <v>563565</v>
       </c>
       <c r="R82" t="n">
-        <v>6968875</v>
+        <v>6968852</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9031,37 +8586,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120724725</v>
+        <v>120724753</v>
       </c>
       <c r="B83" t="n">
-        <v>78333</v>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>228912</v>
+        <v>6464</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9071,10 +8621,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>563580</v>
+        <v>563658</v>
       </c>
       <c r="R83" t="n">
-        <v>6968884</v>
+        <v>6968873</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9133,15 +8683,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>120724709</v>
+        <v>120724713</v>
       </c>
       <c r="B84" t="n">
-        <v>95606</v>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9149,21 +8694,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>53</v>
+        <v>100109</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9173,10 +8718,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>563475</v>
+        <v>563593</v>
       </c>
       <c r="R84" t="n">
-        <v>6968878</v>
+        <v>6968873</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9235,37 +8780,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>120724790</v>
+        <v>120724714</v>
       </c>
       <c r="B85" t="n">
-        <v>79712</v>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9275,10 +8815,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>563565</v>
+        <v>563553</v>
       </c>
       <c r="R85" t="n">
-        <v>6968852</v>
+        <v>6968908</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9337,15 +8877,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>120724769</v>
+        <v>120724715</v>
       </c>
       <c r="B86" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9353,21 +8888,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9377,10 +8912,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>563748</v>
+        <v>563776</v>
       </c>
       <c r="R86" t="n">
-        <v>6968812</v>
+        <v>6968899</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9439,37 +8974,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>120724741</v>
+        <v>120724762</v>
       </c>
       <c r="B87" t="n">
-        <v>79677</v>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9479,10 +9009,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>563480</v>
+        <v>563548</v>
       </c>
       <c r="R87" t="n">
-        <v>6968888</v>
+        <v>6968851</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9541,37 +9071,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>120724760</v>
+        <v>120724763</v>
       </c>
       <c r="B88" t="n">
-        <v>79637</v>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>229497</v>
+        <v>220787</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9581,10 +9106,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>563658</v>
+        <v>563494</v>
       </c>
       <c r="R88" t="n">
-        <v>6968873</v>
+        <v>6968888</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9643,37 +9168,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>120724789</v>
+        <v>120724725</v>
       </c>
       <c r="B89" t="n">
-        <v>91244</v>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>760</v>
+        <v>228912</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9683,10 +9203,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>563829</v>
+        <v>563580</v>
       </c>
       <c r="R89" t="n">
-        <v>6968692</v>
+        <v>6968884</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9742,6 +9262,491 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>120724757</v>
+      </c>
+      <c r="B90" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Lungsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>563709</v>
+      </c>
+      <c r="R90" t="n">
+        <v>6968788</v>
+      </c>
+      <c r="S90" t="n">
+        <v>10</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>120724758</v>
+      </c>
+      <c r="B91" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Lungsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>563565</v>
+      </c>
+      <c r="R91" t="n">
+        <v>6968852</v>
+      </c>
+      <c r="S91" t="n">
+        <v>10</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>120724759</v>
+      </c>
+      <c r="B92" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Lungsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>563518</v>
+      </c>
+      <c r="R92" t="n">
+        <v>6968916</v>
+      </c>
+      <c r="S92" t="n">
+        <v>10</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>120724760</v>
+      </c>
+      <c r="B93" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Lungsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>563658</v>
+      </c>
+      <c r="R93" t="n">
+        <v>6968873</v>
+      </c>
+      <c r="S93" t="n">
+        <v>10</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>120724766</v>
+      </c>
+      <c r="B94" t="n">
+        <v>80398</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>229748</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Gytterlav</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Protopannaria pezizoides</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Lungsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>563783</v>
+      </c>
+      <c r="R94" t="n">
+        <v>6968772</v>
+      </c>
+      <c r="S94" t="n">
+        <v>10</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 51425-2023 artfynd.xlsx
+++ b/artfynd/A 51425-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY94"/>
+  <dimension ref="A1:AZ94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724708</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724709</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724723</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724789</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724707</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724710</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724711</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724712</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111966014</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111966023</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724718</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724719</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1933,6 +1998,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724791</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2030,6 +2100,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724792</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2127,6 +2202,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724793</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2224,6 +2304,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111966057</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2321,6 +2406,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724785</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2418,6 +2508,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724786</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2515,6 +2610,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724787</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2612,6 +2712,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724788</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2710,6 +2815,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724716</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2807,6 +2917,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724704</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2905,6 +3020,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724794</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3002,6 +3122,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111965995</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3099,6 +3224,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111966048</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3209,6 +3339,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17270902</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3306,6 +3441,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724767</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3403,6 +3543,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724768</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3500,6 +3645,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724769</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3597,6 +3747,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724771</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3694,6 +3849,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724772</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3791,6 +3951,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724773</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3888,6 +4053,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724774</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3985,6 +4155,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724775</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4082,6 +4257,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724776</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4179,6 +4359,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724777</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4276,6 +4461,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724778</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4373,6 +4563,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724779</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4470,6 +4665,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724780</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4567,6 +4767,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724781</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4664,6 +4869,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724782</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4761,6 +4971,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724783</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4858,6 +5073,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724784</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -4955,6 +5175,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724705</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5052,6 +5277,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724706</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5149,6 +5379,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724761</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5259,6 +5494,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17270891</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5356,6 +5596,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724720</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5453,6 +5698,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724721</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5550,6 +5800,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724722</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5660,6 +5915,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17270895</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5757,6 +6017,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724726</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5854,6 +6119,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724727</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -5951,6 +6221,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724728</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6048,6 +6323,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724729</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6145,6 +6425,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724730</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6242,6 +6527,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724731</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6339,6 +6629,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724732</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6436,6 +6731,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724733</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6533,6 +6833,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724734</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6630,6 +6935,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724735</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6727,6 +7037,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724736</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6824,6 +7139,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724737</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -6921,6 +7241,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724738</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7018,6 +7343,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724739</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7115,6 +7445,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724740</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7212,6 +7547,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724741</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7309,6 +7649,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724742</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7406,6 +7751,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724743</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7503,6 +7853,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724744</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7600,6 +7955,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724745</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7697,6 +8057,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724746</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -7794,6 +8159,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724747</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -7891,6 +8261,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724748</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -7988,6 +8363,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724749</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8085,6 +8465,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724750</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8182,6 +8567,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724751</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8279,6 +8669,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724752</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8376,6 +8771,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724724</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8486,6 +8886,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17270900</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8583,6 +8988,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724790</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -8680,6 +9090,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724753</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -8777,6 +9192,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724713</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -8874,6 +9294,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724714</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -8971,6 +9396,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724715</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9068,6 +9498,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724762</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9165,6 +9600,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724763</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9262,6 +9702,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724725</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9359,6 +9804,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724757</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9456,6 +9906,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724758</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -9553,6 +10008,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724759</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -9650,6 +10110,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724760</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -9747,8 +10212,108 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724766</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>